--- a/Castor/Calculations/TPS1685_CALC_v2.xlsx
+++ b/Castor/Calculations/TPS1685_CALC_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20359"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0489230\TI Drive\Documents\TPS1685\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eliot\Documents\Power_HW\Castor\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A0621F-FC3E-4AA5-99F0-B7C532FDD660}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210C0C60-4796-41DE-8303-1CF83ECB8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6490" xr2:uid="{286109E9-4905-42EB-8A8D-D32B949EF2D5}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{286109E9-4905-42EB-8A8D-D32B949EF2D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculation Sheet" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1970,45 +1981,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2022,6 +1994,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2036,6 +2011,42 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2112,9 +2123,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2152,7 +2163,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2258,7 +2269,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2400,7 +2411,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2410,39 +2421,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7371F333-15C6-4502-ACA9-B20086E3CA4C}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AA43"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="44.81640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="140.26953125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6328125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="62.54296875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="0.26953125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.36328125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.81640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="27.36328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.08984375" style="4"/>
-    <col min="20" max="25" width="9.08984375" style="2"/>
+    <col min="1" max="1" width="2.47265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.7890625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="140.26171875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="29.5234375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26171875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="4.5234375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7890625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.62890625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="62.5234375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="0.26171875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.3671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.7890625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="27.3671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.3671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1015625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5234375" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.47265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1015625" style="4"/>
+    <col min="20" max="25" width="9.1015625" style="2"/>
     <col min="26" max="27" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.08984375" style="2"/>
+    <col min="28" max="16384" width="9.1015625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="75" t="s">
+    <row r="1" spans="2:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="86"/>
       <c r="J1" s="54"/>
       <c r="K1" s="54"/>
       <c r="L1" s="55"/>
@@ -2460,7 +2471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:27" ht="22.3" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="21"/>
       <c r="C2" s="18"/>
       <c r="D2" s="22"/>
@@ -2478,7 +2489,7 @@
       <c r="S2" s="54"/>
       <c r="AA2" s="5"/>
     </row>
-    <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
       <c r="D3" s="19"/>
@@ -2496,7 +2507,7 @@
       <c r="S3" s="54"/>
       <c r="AA3" s="5"/>
     </row>
-    <row r="4" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="23" t="s">
         <v>1</v>
       </c>
@@ -2526,13 +2537,13 @@
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="78" t="s">
+    <row r="5" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="89"/>
       <c r="J5" s="54"/>
       <c r="K5" s="54"/>
       <c r="L5" s="62"/>
@@ -2545,7 +2556,7 @@
       <c r="S5" s="54"/>
       <c r="AA5" s="5"/>
     </row>
-    <row r="6" spans="2:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:27" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B6" s="26" t="s">
         <v>18</v>
       </c>
@@ -2553,9 +2564,9 @@
         <v>6</v>
       </c>
       <c r="D6" s="74">
-        <v>40</v>
-      </c>
-      <c r="E6" s="85"/>
+        <v>20</v>
+      </c>
+      <c r="E6" s="94"/>
       <c r="J6" s="54"/>
       <c r="K6" s="54"/>
       <c r="L6" s="62"/>
@@ -2570,7 +2581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:27" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B7" s="28" t="s">
         <v>19</v>
       </c>
@@ -2578,9 +2589,9 @@
         <v>8</v>
       </c>
       <c r="D7" s="51">
-        <v>54</v>
-      </c>
-      <c r="E7" s="86"/>
+        <v>26</v>
+      </c>
+      <c r="E7" s="79"/>
       <c r="J7" s="54"/>
       <c r="K7" s="54"/>
       <c r="L7" s="62"/>
@@ -2593,7 +2604,7 @@
       <c r="S7" s="54"/>
       <c r="AA7" s="5"/>
     </row>
-    <row r="8" spans="2:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B8" s="29" t="s">
         <v>20</v>
       </c>
@@ -2601,9 +2612,9 @@
         <v>9</v>
       </c>
       <c r="D8" s="52">
-        <v>60</v>
-      </c>
-      <c r="E8" s="86"/>
+        <v>30</v>
+      </c>
+      <c r="E8" s="79"/>
       <c r="J8" s="54"/>
       <c r="K8" s="54"/>
       <c r="L8" s="62"/>
@@ -2611,11 +2622,11 @@
       <c r="N8" s="63"/>
       <c r="O8" s="56"/>
       <c r="P8" s="54"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-    </row>
-    <row r="9" spans="2:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+    </row>
+    <row r="9" spans="2:27" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B9" s="28" t="s">
         <v>21</v>
       </c>
@@ -2623,9 +2634,9 @@
         <v>10</v>
       </c>
       <c r="D9" s="52">
-        <v>45</v>
-      </c>
-      <c r="E9" s="86"/>
+        <v>20</v>
+      </c>
+      <c r="E9" s="79"/>
       <c r="J9" s="54"/>
       <c r="K9" s="54"/>
       <c r="L9" s="62"/>
@@ -2633,11 +2644,11 @@
       <c r="N9" s="63"/>
       <c r="O9" s="56"/>
       <c r="P9" s="54"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+    </row>
+    <row r="10" spans="2:27" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B10" s="28" t="s">
         <v>22</v>
       </c>
@@ -2645,9 +2656,9 @@
         <v>11</v>
       </c>
       <c r="D10" s="51">
-        <v>2000</v>
-      </c>
-      <c r="E10" s="86"/>
+        <v>10000</v>
+      </c>
+      <c r="E10" s="79"/>
       <c r="J10" s="54"/>
       <c r="K10" s="54"/>
       <c r="L10" s="62"/>
@@ -2655,11 +2666,11 @@
       <c r="N10" s="63"/>
       <c r="O10" s="56"/>
       <c r="P10" s="54"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-    </row>
-    <row r="11" spans="2:27" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+    </row>
+    <row r="11" spans="2:27" ht="18.899999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="31" t="s">
         <v>23</v>
       </c>
@@ -2669,7 +2680,7 @@
       <c r="D11" s="53">
         <v>55</v>
       </c>
-      <c r="E11" s="87"/>
+      <c r="E11" s="95"/>
       <c r="J11" s="54"/>
       <c r="K11" s="54"/>
       <c r="L11" s="62"/>
@@ -2677,11 +2688,11 @@
       <c r="N11" s="63"/>
       <c r="O11" s="56"/>
       <c r="P11" s="54"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-    </row>
-    <row r="12" spans="2:27" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+    </row>
+    <row r="12" spans="2:27" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B12" s="33"/>
       <c r="C12" s="33"/>
       <c r="D12" s="22"/>
@@ -2694,17 +2705,17 @@
       <c r="N12" s="54"/>
       <c r="O12" s="54"/>
       <c r="P12" s="54"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-    </row>
-    <row r="13" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="82" t="s">
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+    </row>
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="84"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
       <c r="F13" s="7"/>
       <c r="J13" s="54"/>
       <c r="K13" s="54"/>
@@ -2717,7 +2728,7 @@
       <c r="R13" s="54"/>
       <c r="S13" s="54"/>
     </row>
-    <row r="14" spans="2:27" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:27" ht="30.55" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="43" t="s">
         <v>50</v>
       </c>
@@ -2726,9 +2737,9 @@
       </c>
       <c r="D14" s="36">
         <f>ROUNDUP((D9/20),0)</f>
-        <v>3</v>
-      </c>
-      <c r="E14" s="91"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="78"/>
       <c r="J14" s="54"/>
       <c r="K14" s="54"/>
       <c r="L14" s="56"/>
@@ -2740,15 +2751,15 @@
       <c r="R14" s="54"/>
       <c r="S14" s="54"/>
     </row>
-    <row r="15" spans="2:27" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="88" t="s">
+    <row r="15" spans="2:27" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="89"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="36">
-        <v>3</v>
-      </c>
-      <c r="E15" s="86"/>
+        <v>1</v>
+      </c>
+      <c r="E15" s="79"/>
       <c r="J15" s="54"/>
       <c r="K15" s="54"/>
       <c r="L15" s="56"/>
@@ -2760,7 +2771,7 @@
       <c r="R15" s="54"/>
       <c r="S15" s="54"/>
     </row>
-    <row r="16" spans="2:27" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:27" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="45" t="s">
         <v>24</v>
       </c>
@@ -2770,7 +2781,7 @@
       <c r="D16" s="37">
         <v>55</v>
       </c>
-      <c r="E16" s="92"/>
+      <c r="E16" s="80"/>
       <c r="F16" s="8"/>
       <c r="J16" s="64"/>
       <c r="K16" s="64"/>
@@ -2783,7 +2794,7 @@
       <c r="R16" s="64"/>
       <c r="S16" s="64"/>
     </row>
-    <row r="17" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="45" t="s">
         <v>25</v>
       </c>
@@ -2793,7 +2804,7 @@
       <c r="D17" s="37">
         <v>1</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="E17" s="77" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="8"/>
@@ -2808,7 +2819,7 @@
       <c r="R17" s="64"/>
       <c r="S17" s="64"/>
     </row>
-    <row r="18" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="45" t="s">
         <v>68</v>
       </c>
@@ -2819,7 +2830,7 @@
         <f>((D17*10^3/25))</f>
         <v>40</v>
       </c>
-      <c r="E18" s="90"/>
+      <c r="E18" s="77"/>
       <c r="F18" s="8"/>
       <c r="J18" s="64"/>
       <c r="K18" s="64"/>
@@ -2832,7 +2843,7 @@
       <c r="R18" s="64"/>
       <c r="S18" s="64"/>
     </row>
-    <row r="19" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="45" t="s">
         <v>69</v>
       </c>
@@ -2842,7 +2853,7 @@
       <c r="D19" s="38">
         <v>40.200000000000003</v>
       </c>
-      <c r="E19" s="90"/>
+      <c r="E19" s="77"/>
       <c r="F19" s="8"/>
       <c r="J19" s="64"/>
       <c r="K19" s="64"/>
@@ -2855,7 +2866,7 @@
       <c r="R19" s="64"/>
       <c r="S19" s="64"/>
     </row>
-    <row r="20" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="45" t="s">
         <v>70</v>
       </c>
@@ -2866,7 +2877,7 @@
         <f>(D19*1000*25*10^-6)</f>
         <v>1.0049999999999999</v>
       </c>
-      <c r="E20" s="90"/>
+      <c r="E20" s="77"/>
       <c r="F20" s="8" t="s">
         <v>14</v>
       </c>
@@ -2881,7 +2892,7 @@
       <c r="R20" s="64"/>
       <c r="S20" s="64"/>
     </row>
-    <row r="21" spans="2:19" s="9" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" s="9" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="45" t="s">
         <v>26</v>
       </c>
@@ -2892,7 +2903,7 @@
         <f>(D20)/(D16*18.38*10^-6)</f>
         <v>994.16361657928576</v>
       </c>
-      <c r="E21" s="90" t="s">
+      <c r="E21" s="77" t="s">
         <v>48</v>
       </c>
       <c r="F21" s="8"/>
@@ -2907,7 +2918,7 @@
       <c r="R21" s="64"/>
       <c r="S21" s="64"/>
     </row>
-    <row r="22" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="45" t="s">
         <v>27</v>
       </c>
@@ -2917,7 +2928,7 @@
       <c r="D22" s="38">
         <v>1000</v>
       </c>
-      <c r="E22" s="90"/>
+      <c r="E22" s="77"/>
       <c r="F22" s="8"/>
       <c r="J22" s="64"/>
       <c r="K22" s="64"/>
@@ -2930,7 +2941,7 @@
       <c r="R22" s="64"/>
       <c r="S22" s="64"/>
     </row>
-    <row r="23" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="45" t="s">
         <v>28</v>
       </c>
@@ -2941,7 +2952,7 @@
         <f>(D20)/(18.38*10^-6*D22)</f>
         <v>54.678998911860724</v>
       </c>
-      <c r="E23" s="90"/>
+      <c r="E23" s="77"/>
       <c r="F23" s="8"/>
       <c r="J23" s="64"/>
       <c r="K23" s="64"/>
@@ -2954,7 +2965,7 @@
       <c r="R23" s="64"/>
       <c r="S23" s="64"/>
     </row>
-    <row r="24" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="48" t="s">
         <v>71</v>
       </c>
@@ -2963,13 +2974,13 @@
       </c>
       <c r="D24" s="40">
         <f>(1.1/3)*D15*D22</f>
-        <v>1100</v>
-      </c>
-      <c r="E24" s="93"/>
+        <v>366.66666666666669</v>
+      </c>
+      <c r="E24" s="81"/>
       <c r="F24" s="8"/>
       <c r="L24" s="10"/>
     </row>
-    <row r="25" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="48" t="s">
         <v>72</v>
       </c>
@@ -2979,11 +2990,11 @@
       <c r="D25" s="39">
         <v>1100</v>
       </c>
-      <c r="E25" s="94"/>
+      <c r="E25" s="82"/>
       <c r="F25" s="8"/>
       <c r="L25" s="10"/>
     </row>
-    <row r="26" spans="2:19" s="9" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="48" t="s">
         <v>77</v>
       </c>
@@ -2994,11 +3005,11 @@
         <f>(1.1*D20)/(3*18.26*10^-6*D25)</f>
         <v>18.346111719605695</v>
       </c>
-      <c r="E26" s="94"/>
+      <c r="E26" s="82"/>
       <c r="F26" s="8"/>
       <c r="L26" s="10"/>
     </row>
-    <row r="27" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="45" t="s">
         <v>29</v>
       </c>
@@ -3008,11 +3019,11 @@
       <c r="D27" s="37">
         <v>2</v>
       </c>
-      <c r="E27" s="94"/>
+      <c r="E27" s="82"/>
       <c r="F27" s="8"/>
       <c r="L27" s="10"/>
     </row>
-    <row r="28" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="45" t="s">
         <v>73</v>
       </c>
@@ -3023,11 +3034,11 @@
         <f>(D27*2/1.54)</f>
         <v>2.5974025974025974</v>
       </c>
-      <c r="E28" s="94"/>
+      <c r="E28" s="82"/>
       <c r="F28" s="8"/>
       <c r="L28" s="10"/>
     </row>
-    <row r="29" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="45" t="s">
         <v>74</v>
       </c>
@@ -3037,11 +3048,11 @@
       <c r="D29" s="38">
         <v>3.3</v>
       </c>
-      <c r="E29" s="94"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="8"/>
       <c r="L29" s="10"/>
     </row>
-    <row r="30" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="45" t="s">
         <v>75</v>
       </c>
@@ -3052,13 +3063,13 @@
         <f>(D29*1.54/2)</f>
         <v>2.5409999999999999</v>
       </c>
-      <c r="E30" s="94"/>
+      <c r="E30" s="82"/>
       <c r="F30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="L30" s="10"/>
     </row>
-    <row r="31" spans="2:19" s="9" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="45" t="s">
         <v>32</v>
       </c>
@@ -3068,11 +3079,11 @@
       <c r="D31" s="37">
         <v>60</v>
       </c>
-      <c r="E31" s="94"/>
+      <c r="E31" s="82"/>
       <c r="F31" s="8"/>
       <c r="L31" s="10"/>
     </row>
-    <row r="32" spans="2:19" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="45" t="s">
         <v>33</v>
       </c>
@@ -3081,15 +3092,15 @@
       </c>
       <c r="D32" s="36">
         <f>48/(D7/D31)</f>
-        <v>53.333333333333329</v>
-      </c>
-      <c r="E32" s="94"/>
+        <v>110.76923076923076</v>
+      </c>
+      <c r="E32" s="82"/>
       <c r="L32" s="6"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="45" t="s">
         <v>34</v>
       </c>
@@ -3099,13 +3110,13 @@
       <c r="D33" s="36">
         <v>56</v>
       </c>
-      <c r="E33" s="94"/>
+      <c r="E33" s="82"/>
       <c r="L33" s="6"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="45" t="s">
         <v>35</v>
       </c>
@@ -3114,15 +3125,15 @@
       </c>
       <c r="D34" s="36">
         <f>D7/(48/D33)</f>
-        <v>63</v>
-      </c>
-      <c r="E34" s="94"/>
+        <v>30.333333333333336</v>
+      </c>
+      <c r="E34" s="82"/>
       <c r="L34" s="6"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="45" t="s">
         <v>38</v>
       </c>
@@ -3131,15 +3142,15 @@
       </c>
       <c r="D35" s="40">
         <f>D10*D7/(D34*1000)</f>
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="E35" s="95"/>
+        <v>8.5714285714285712</v>
+      </c>
+      <c r="E35" s="83"/>
       <c r="L35" s="6"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="45" t="s">
         <v>43</v>
       </c>
@@ -3155,7 +3166,7 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="45" t="s">
         <v>41</v>
       </c>
@@ -3164,7 +3175,7 @@
       </c>
       <c r="D37" s="40">
         <f>D36*1.2/(D6-1.2)</f>
-        <v>30.927835051546396</v>
+        <v>63.829787234042549</v>
       </c>
       <c r="E37" s="35"/>
       <c r="L37" s="6"/>
@@ -3172,7 +3183,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B38" s="45" t="s">
         <v>42</v>
       </c>
@@ -3180,7 +3191,7 @@
         <v>46</v>
       </c>
       <c r="D38" s="41">
-        <v>31</v>
+        <v>63.8</v>
       </c>
       <c r="E38" s="35"/>
       <c r="L38" s="11"/>
@@ -3191,7 +3202,7 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
     </row>
-    <row r="39" spans="1:19" s="12" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" s="12" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2"/>
       <c r="B39" s="45" t="s">
         <v>40</v>
@@ -3201,7 +3212,7 @@
       </c>
       <c r="D39" s="70">
         <f>1.2*(D36+D38)/D38</f>
-        <v>39.909677419354843</v>
+        <v>20.008777429467084</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="1"/>
@@ -3209,7 +3220,7 @@
       <c r="R39" s="13"/>
       <c r="S39" s="14"/>
     </row>
-    <row r="40" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="66" t="s">
         <v>55</v>
       </c>
@@ -3225,7 +3236,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="45" t="s">
         <v>57</v>
       </c>
@@ -3234,7 +3245,7 @@
       </c>
       <c r="D41" s="40">
         <f>D40*1.164/(D8-1.164)</f>
-        <v>19.78380583316337</v>
+        <v>40.366208905534748</v>
       </c>
       <c r="E41" s="35"/>
       <c r="L41" s="6"/>
@@ -3242,7 +3253,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" ht="18.600000000000001" x14ac:dyDescent="0.5">
       <c r="B42" s="45" t="s">
         <v>58</v>
       </c>
@@ -3250,7 +3261,7 @@
         <v>61</v>
       </c>
       <c r="D42" s="41">
-        <v>20</v>
+        <v>40.4</v>
       </c>
       <c r="E42" s="35"/>
       <c r="L42" s="11"/>
@@ -3261,7 +3272,7 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
     </row>
-    <row r="43" spans="1:19" s="12" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:19" s="12" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A43" s="2"/>
       <c r="B43" s="49" t="s">
         <v>59</v>
@@ -3271,7 +3282,7 @@
       </c>
       <c r="D43" s="42">
         <f>1.164*(D40+D42)/D42</f>
-        <v>59.363999999999997</v>
+        <v>29.975881188118812</v>
       </c>
       <c r="E43" s="34"/>
       <c r="F43" s="1"/>
@@ -3285,16 +3296,16 @@
     <protectedRange sqref="D14:D19 D6:D12 D27:D29 D21:D23" name="UserInputs"/>
   </protectedRanges>
   <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="Q8:S12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="E6:E11"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="E17:E20"/>
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="E14:E16"/>
     <mergeCell ref="E24:E35"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="Q8:S12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="E6:E11"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThan" showInputMessage="1" showErrorMessage="1" errorTitle="ERROR!!" error="Start-up Load Resistor is &lt; VCC(max)/Imax, this will prevent start-up." prompt="Rload must be &gt; VCC(max)/Imax" sqref="D12" xr:uid="{85779163-166E-4A04-8914-8F3697CEB48B}">
